--- a/artfynd/A 40918-2024 artfynd.xlsx
+++ b/artfynd/A 40918-2024 artfynd.xlsx
@@ -1512,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121087376</v>
+        <v>121087515</v>
       </c>
       <c r="B9" t="n">
-        <v>78598</v>
+        <v>57348</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,37 +1528,45 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541741</v>
+        <v>541449</v>
       </c>
       <c r="R9" t="n">
-        <v>7207555</v>
+        <v>7207320</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1587,7 +1595,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1605,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,19 +1620,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121087515</v>
+        <v>121087368</v>
       </c>
       <c r="B10" t="n">
         <v>57348</v>
@@ -1658,27 +1666,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541449</v>
+        <v>541804</v>
       </c>
       <c r="R10" t="n">
-        <v>7207320</v>
+        <v>7207640</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1707,7 +1712,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1717,7 +1722,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,22 +1737,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121087368</v>
+        <v>121087376</v>
       </c>
       <c r="B11" t="n">
-        <v>57348</v>
+        <v>78598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,39 +1765,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541804</v>
+        <v>541741</v>
       </c>
       <c r="R11" t="n">
-        <v>7207640</v>
+        <v>7207555</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3019,10 +3019,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121086339</v>
+        <v>121087370</v>
       </c>
       <c r="B22" t="n">
-        <v>57348</v>
+        <v>94474</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3031,49 +3031,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541803</v>
+        <v>541805</v>
       </c>
       <c r="R22" t="n">
-        <v>7207589</v>
+        <v>7207635</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3102,7 +3094,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3112,12 +3104,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3128,46 +3115,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121086340</v>
+        <v>121087271</v>
       </c>
       <c r="B23" t="n">
-        <v>90973</v>
+        <v>94474</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3176,44 +3143,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541758</v>
+        <v>541696</v>
       </c>
       <c r="R23" t="n">
-        <v>7207515</v>
+        <v>7207589</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3242,7 +3206,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3252,12 +3216,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:56</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>på granlåga med bark</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3266,54 +3225,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121087370</v>
+        <v>121086339</v>
       </c>
       <c r="B24" t="n">
-        <v>94474</v>
+        <v>57348</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3322,41 +3255,49 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541805</v>
+        <v>541803</v>
       </c>
       <c r="R24" t="n">
-        <v>7207635</v>
+        <v>7207589</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3385,7 +3326,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3395,7 +3336,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3406,26 +3352,46 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121087271</v>
+        <v>121086340</v>
       </c>
       <c r="B25" t="n">
-        <v>94474</v>
+        <v>90973</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3434,41 +3400,44 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541696</v>
+        <v>541758</v>
       </c>
       <c r="R25" t="n">
-        <v>7207589</v>
+        <v>7207515</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3497,7 +3466,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3507,7 +3476,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>på granlåga med bark</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3516,28 +3490,54 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121087378</v>
+        <v>121087379</v>
       </c>
       <c r="B26" t="n">
-        <v>78598</v>
+        <v>57348</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3550,34 +3550,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541709</v>
+        <v>541665</v>
       </c>
       <c r="R26" t="n">
-        <v>7207545</v>
+        <v>7207481</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3609,7 +3614,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3619,7 +3624,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3646,10 +3651,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121087377</v>
+        <v>121087378</v>
       </c>
       <c r="B27" t="n">
-        <v>90652</v>
+        <v>78598</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3658,25 +3663,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3758,10 +3763,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121087379</v>
+        <v>121087377</v>
       </c>
       <c r="B28" t="n">
-        <v>57348</v>
+        <v>90652</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3770,43 +3775,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541665</v>
+        <v>541709</v>
       </c>
       <c r="R28" t="n">
-        <v>7207481</v>
+        <v>7207545</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 40918-2024 artfynd.xlsx
+++ b/artfynd/A 40918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121087269</v>
+        <v>121087372</v>
       </c>
       <c r="B2" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541501</v>
+        <v>541765</v>
       </c>
       <c r="R2" t="n">
-        <v>7207540</v>
+        <v>7207562</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121087174</v>
+        <v>121087378</v>
       </c>
       <c r="B3" t="n">
-        <v>90705</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,40 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541827</v>
+        <v>541709</v>
       </c>
       <c r="R3" t="n">
-        <v>7207629</v>
+        <v>7207545</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,29 +886,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121087369</v>
+        <v>121087377</v>
       </c>
       <c r="B4" t="n">
-        <v>57348</v>
+        <v>90662</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,43 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541805</v>
+        <v>541709</v>
       </c>
       <c r="R4" t="n">
-        <v>7207638</v>
+        <v>7207545</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121087383</v>
+        <v>121086339</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,37 +1032,45 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541686</v>
+        <v>541803</v>
       </c>
       <c r="R5" t="n">
-        <v>7207278</v>
+        <v>7207589</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1109,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,26 +1125,46 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121087371</v>
+        <v>121087383</v>
       </c>
       <c r="B6" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,39 +1177,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541769</v>
+        <v>541686</v>
       </c>
       <c r="R6" t="n">
-        <v>7207584</v>
+        <v>7207278</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121087372</v>
+        <v>121087174</v>
       </c>
       <c r="B7" t="n">
-        <v>57348</v>
+        <v>90715</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,42 +1289,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541765</v>
+        <v>541827</v>
       </c>
       <c r="R7" t="n">
-        <v>7207562</v>
+        <v>7207629</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,28 +1370,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121086345</v>
+        <v>121087270</v>
       </c>
       <c r="B8" t="n">
-        <v>90683</v>
+        <v>90662</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,44 +1401,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541754</v>
+        <v>541639</v>
       </c>
       <c r="R8" t="n">
-        <v>7207520</v>
+        <v>7207569</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,7 +1464,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,12 +1474,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>på levande gran</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,54 +1483,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121087515</v>
+        <v>121087267</v>
       </c>
       <c r="B9" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,45 +1517,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541449</v>
+        <v>541478</v>
       </c>
       <c r="R9" t="n">
-        <v>7207320</v>
+        <v>7207309</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1595,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1605,7 +1586,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,22 +1601,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121087368</v>
+        <v>121087376</v>
       </c>
       <c r="B10" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1648,39 +1629,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541804</v>
+        <v>541741</v>
       </c>
       <c r="R10" t="n">
-        <v>7207640</v>
+        <v>7207555</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1712,7 +1688,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1722,7 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121087376</v>
+        <v>121087367</v>
       </c>
       <c r="B11" t="n">
-        <v>78598</v>
+        <v>90715</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1765,21 +1741,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1789,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541741</v>
+        <v>541803</v>
       </c>
       <c r="R11" t="n">
-        <v>7207555</v>
+        <v>7207639</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1824,7 +1800,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1834,7 +1810,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121087385</v>
+        <v>121086340</v>
       </c>
       <c r="B12" t="n">
-        <v>78598</v>
+        <v>90983</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,37 +1853,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541689</v>
+        <v>541758</v>
       </c>
       <c r="R12" t="n">
-        <v>7207232</v>
+        <v>7207515</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1936,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1946,7 +1925,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>på granlåga med bark</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,28 +1939,54 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121087270</v>
+        <v>121087266</v>
       </c>
       <c r="B13" t="n">
-        <v>90652</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,25 +1995,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2013,10 +2023,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541639</v>
+        <v>541464</v>
       </c>
       <c r="R13" t="n">
-        <v>7207569</v>
+        <v>7207278</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2048,7 +2058,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2058,7 +2068,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2085,10 +2095,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121087384</v>
+        <v>121087271</v>
       </c>
       <c r="B14" t="n">
-        <v>57348</v>
+        <v>94484</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2097,43 +2107,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541683</v>
+        <v>541696</v>
       </c>
       <c r="R14" t="n">
-        <v>7207222</v>
+        <v>7207589</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2165,7 +2170,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2175,7 +2180,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2202,10 +2207,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121087367</v>
+        <v>121087385</v>
       </c>
       <c r="B15" t="n">
-        <v>90705</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2218,21 +2223,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2242,10 +2247,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541803</v>
+        <v>541689</v>
       </c>
       <c r="R15" t="n">
-        <v>7207639</v>
+        <v>7207232</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2277,7 +2282,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2287,7 +2292,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2314,10 +2319,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121086338</v>
+        <v>121087375</v>
       </c>
       <c r="B16" t="n">
-        <v>57348</v>
+        <v>90693</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2330,45 +2335,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541797</v>
+        <v>541743</v>
       </c>
       <c r="R16" t="n">
-        <v>7207596</v>
+        <v>7207555</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2397,7 +2394,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2407,12 +2404,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2423,36 +2415,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2462,7 +2434,7 @@
         <v>121087373</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2571,10 +2543,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121087380</v>
+        <v>121087515</v>
       </c>
       <c r="B18" t="n">
-        <v>90683</v>
+        <v>57351</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2587,37 +2559,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541639</v>
+        <v>541449</v>
       </c>
       <c r="R18" t="n">
-        <v>7207443</v>
+        <v>7207320</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2646,7 +2626,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2656,7 +2636,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2671,22 +2651,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121087266</v>
+        <v>121087380</v>
       </c>
       <c r="B19" t="n">
-        <v>78598</v>
+        <v>90693</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2699,21 +2679,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2723,10 +2703,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541464</v>
+        <v>541639</v>
       </c>
       <c r="R19" t="n">
-        <v>7207278</v>
+        <v>7207443</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2758,7 +2738,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2768,7 +2748,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2798,7 +2778,7 @@
         <v>121087382</v>
       </c>
       <c r="B20" t="n">
-        <v>74705</v>
+        <v>74708</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2907,10 +2887,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121087375</v>
+        <v>121087269</v>
       </c>
       <c r="B21" t="n">
-        <v>90683</v>
+        <v>90715</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2923,21 +2903,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2947,10 +2927,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541743</v>
+        <v>541501</v>
       </c>
       <c r="R21" t="n">
-        <v>7207555</v>
+        <v>7207540</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2982,7 +2962,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2992,7 +2972,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3019,10 +2999,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121087370</v>
+        <v>121087374</v>
       </c>
       <c r="B22" t="n">
-        <v>94474</v>
+        <v>57351</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3031,38 +3011,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541805</v>
+        <v>541748</v>
       </c>
       <c r="R22" t="n">
-        <v>7207635</v>
+        <v>7207555</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3094,7 +3079,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3104,7 +3089,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3131,10 +3116,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121087271</v>
+        <v>121087379</v>
       </c>
       <c r="B23" t="n">
-        <v>94474</v>
+        <v>57351</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3143,38 +3128,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541696</v>
+        <v>541665</v>
       </c>
       <c r="R23" t="n">
-        <v>7207589</v>
+        <v>7207481</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3206,7 +3196,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3216,7 +3206,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3243,10 +3233,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121086339</v>
+        <v>121087369</v>
       </c>
       <c r="B24" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3277,27 +3267,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541803</v>
+        <v>541805</v>
       </c>
       <c r="R24" t="n">
-        <v>7207589</v>
+        <v>7207638</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3326,7 +3313,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3336,12 +3323,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3352,46 +3334,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121086340</v>
+        <v>121087368</v>
       </c>
       <c r="B25" t="n">
-        <v>90973</v>
+        <v>57351</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3404,40 +3366,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541758</v>
+        <v>541804</v>
       </c>
       <c r="R25" t="n">
-        <v>7207515</v>
+        <v>7207640</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3466,7 +3430,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3476,12 +3440,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:56</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>på granlåga med bark</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3490,54 +3449,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121087379</v>
+        <v>121086345</v>
       </c>
       <c r="B26" t="n">
-        <v>57348</v>
+        <v>90693</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3550,42 +3483,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541665</v>
+        <v>541754</v>
       </c>
       <c r="R26" t="n">
-        <v>7207481</v>
+        <v>7207520</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3614,7 +3545,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3624,7 +3555,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>på levande gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3633,28 +3569,54 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121087378</v>
+        <v>121087371</v>
       </c>
       <c r="B27" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3667,34 +3629,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541709</v>
+        <v>541769</v>
       </c>
       <c r="R27" t="n">
-        <v>7207545</v>
+        <v>7207584</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3726,7 +3693,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3736,7 +3703,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3763,10 +3730,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121087377</v>
+        <v>121087370</v>
       </c>
       <c r="B28" t="n">
-        <v>90652</v>
+        <v>94484</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3779,21 +3746,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3803,10 +3770,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541709</v>
+        <v>541805</v>
       </c>
       <c r="R28" t="n">
-        <v>7207545</v>
+        <v>7207635</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3838,7 +3805,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3848,7 +3815,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3875,10 +3842,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121087267</v>
+        <v>121087384</v>
       </c>
       <c r="B29" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3891,34 +3858,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541478</v>
+        <v>541683</v>
       </c>
       <c r="R29" t="n">
-        <v>7207309</v>
+        <v>7207222</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3950,7 +3922,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3960,7 +3932,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3987,10 +3959,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121087374</v>
+        <v>121086338</v>
       </c>
       <c r="B30" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4021,24 +3993,27 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541748</v>
+        <v>541797</v>
       </c>
       <c r="R30" t="n">
-        <v>7207555</v>
+        <v>7207596</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4067,7 +4042,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4077,7 +4052,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4088,16 +4068,36 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 40918-2024 artfynd.xlsx
+++ b/artfynd/A 40918-2024 artfynd.xlsx
@@ -1501,7 +1501,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121087267</v>
+        <v>121087376</v>
       </c>
       <c r="B9" t="n">
         <v>78601</v>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541478</v>
+        <v>541741</v>
       </c>
       <c r="R9" t="n">
-        <v>7207309</v>
+        <v>7207555</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121087376</v>
+        <v>121087367</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541741</v>
+        <v>541803</v>
       </c>
       <c r="R10" t="n">
-        <v>7207555</v>
+        <v>7207639</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121087367</v>
+        <v>121086340</v>
       </c>
       <c r="B11" t="n">
-        <v>90715</v>
+        <v>90983</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,37 +1741,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541803</v>
+        <v>541758</v>
       </c>
       <c r="R11" t="n">
-        <v>7207639</v>
+        <v>7207515</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1800,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1810,7 +1813,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>på granlåga med bark</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,28 +1827,54 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121086340</v>
+        <v>121087267</v>
       </c>
       <c r="B12" t="n">
-        <v>90983</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,40 +1887,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541758</v>
+        <v>541478</v>
       </c>
       <c r="R12" t="n">
-        <v>7207515</v>
+        <v>7207309</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1915,7 +1946,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,12 +1956,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:56</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>på granlåga med bark</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,44 +1965,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 40918-2024 artfynd.xlsx
+++ b/artfynd/A 40918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121087372</v>
+        <v>121087378</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541765</v>
+        <v>541709</v>
       </c>
       <c r="R2" t="n">
-        <v>7207562</v>
+        <v>7207545</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121087378</v>
+        <v>121087372</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541709</v>
+        <v>541765</v>
       </c>
       <c r="R3" t="n">
-        <v>7207545</v>
+        <v>7207562</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1501,7 +1501,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121087376</v>
+        <v>121087267</v>
       </c>
       <c r="B9" t="n">
         <v>78601</v>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541741</v>
+        <v>541478</v>
       </c>
       <c r="R9" t="n">
-        <v>7207555</v>
+        <v>7207309</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121087367</v>
+        <v>121087376</v>
       </c>
       <c r="B10" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541803</v>
+        <v>541741</v>
       </c>
       <c r="R10" t="n">
-        <v>7207639</v>
+        <v>7207555</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121086340</v>
+        <v>121087367</v>
       </c>
       <c r="B11" t="n">
-        <v>90983</v>
+        <v>90715</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,40 +1741,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541758</v>
+        <v>541803</v>
       </c>
       <c r="R11" t="n">
-        <v>7207515</v>
+        <v>7207639</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1803,7 +1800,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,12 +1810,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:56</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>på granlåga med bark</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,54 +1819,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121087267</v>
+        <v>121086340</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>90983</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,37 +1853,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541478</v>
+        <v>541758</v>
       </c>
       <c r="R12" t="n">
-        <v>7207309</v>
+        <v>7207515</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1946,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1956,7 +1925,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>på granlåga med bark</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,18 +1939,44 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121087373</v>
+        <v>121087380</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>90693</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541765</v>
+        <v>541639</v>
       </c>
       <c r="R17" t="n">
-        <v>7207564</v>
+        <v>7207443</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2543,10 +2543,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121087515</v>
+        <v>121087373</v>
       </c>
       <c r="B18" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2559,45 +2559,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541449</v>
+        <v>541765</v>
       </c>
       <c r="R18" t="n">
-        <v>7207320</v>
+        <v>7207564</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2626,7 +2618,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2636,7 +2628,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2651,22 +2643,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121087380</v>
+        <v>121087515</v>
       </c>
       <c r="B19" t="n">
-        <v>90693</v>
+        <v>57351</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,37 +2671,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541639</v>
+        <v>541449</v>
       </c>
       <c r="R19" t="n">
-        <v>7207443</v>
+        <v>7207320</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2763,12 +2763,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 40918-2024 artfynd.xlsx
+++ b/artfynd/A 40918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121087378</v>
+        <v>121087174</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541709</v>
+        <v>541827</v>
       </c>
       <c r="R2" t="n">
-        <v>7207545</v>
+        <v>7207629</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,28 +772,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121087372</v>
+        <v>121087383</v>
       </c>
       <c r="B3" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541765</v>
+        <v>541686</v>
       </c>
       <c r="R3" t="n">
-        <v>7207562</v>
+        <v>7207278</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121087377</v>
+        <v>121086338</v>
       </c>
       <c r="B4" t="n">
-        <v>90662</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,41 +915,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541709</v>
+        <v>541797</v>
       </c>
       <c r="R4" t="n">
-        <v>7207545</v>
+        <v>7207596</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +996,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,23 +1012,43 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121086339</v>
+        <v>121087369</v>
       </c>
       <c r="B5" t="n">
         <v>57351</v>
@@ -1050,27 +1082,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541803</v>
+        <v>541805</v>
       </c>
       <c r="R5" t="n">
-        <v>7207589</v>
+        <v>7207638</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,12 +1138,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,46 +1149,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121087383</v>
+        <v>121087368</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,34 +1181,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541686</v>
+        <v>541804</v>
       </c>
       <c r="R6" t="n">
-        <v>7207278</v>
+        <v>7207640</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1236,7 +1245,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1255,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121087174</v>
+        <v>121087270</v>
       </c>
       <c r="B7" t="n">
-        <v>90715</v>
+        <v>90662</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,44 +1294,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541827</v>
+        <v>541639</v>
       </c>
       <c r="R7" t="n">
-        <v>7207629</v>
+        <v>7207569</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,7 +1357,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,7 +1367,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,26 +1376,25 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121087270</v>
+        <v>121087377</v>
       </c>
       <c r="B8" t="n">
         <v>90662</v>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541639</v>
+        <v>541709</v>
       </c>
       <c r="R8" t="n">
-        <v>7207569</v>
+        <v>7207545</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1464,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1474,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,7 +1506,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121087267</v>
+        <v>121087373</v>
       </c>
       <c r="B9" t="n">
         <v>78601</v>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541478</v>
+        <v>541765</v>
       </c>
       <c r="R9" t="n">
-        <v>7207309</v>
+        <v>7207564</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1576,7 +1581,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,7 +1591,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121087376</v>
+        <v>121087367</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,21 +1634,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,10 +1658,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541741</v>
+        <v>541803</v>
       </c>
       <c r="R10" t="n">
-        <v>7207555</v>
+        <v>7207639</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1688,7 +1693,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,7 +1703,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121087367</v>
+        <v>121087266</v>
       </c>
       <c r="B11" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,21 +1746,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1770,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541803</v>
+        <v>541464</v>
       </c>
       <c r="R11" t="n">
-        <v>7207639</v>
+        <v>7207278</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1800,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1810,7 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121086340</v>
+        <v>121087375</v>
       </c>
       <c r="B12" t="n">
-        <v>90983</v>
+        <v>90693</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,40 +1858,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541758</v>
+        <v>541743</v>
       </c>
       <c r="R12" t="n">
-        <v>7207515</v>
+        <v>7207555</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1915,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,12 +1927,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:56</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>på granlåga med bark</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,54 +1936,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121087266</v>
+        <v>121087379</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,34 +1970,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541464</v>
+        <v>541665</v>
       </c>
       <c r="R13" t="n">
-        <v>7207278</v>
+        <v>7207481</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2058,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2068,7 +2044,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,10 +2071,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121087271</v>
+        <v>121086339</v>
       </c>
       <c r="B14" t="n">
-        <v>94484</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,41 +2083,49 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541696</v>
+        <v>541803</v>
       </c>
       <c r="R14" t="n">
         <v>7207589</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2170,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2180,7 +2164,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,26 +2180,46 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121087385</v>
+        <v>121087374</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2223,34 +2232,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541689</v>
+        <v>541748</v>
       </c>
       <c r="R15" t="n">
-        <v>7207232</v>
+        <v>7207555</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2282,7 +2296,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2292,7 +2306,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2319,7 +2333,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121087375</v>
+        <v>121086345</v>
       </c>
       <c r="B16" t="n">
         <v>90693</v>
@@ -2353,19 +2367,22 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541743</v>
+        <v>541754</v>
       </c>
       <c r="R16" t="n">
-        <v>7207555</v>
+        <v>7207520</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2394,7 +2411,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2404,7 +2421,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>på levande gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2413,28 +2435,54 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121087380</v>
+        <v>121087370</v>
       </c>
       <c r="B17" t="n">
-        <v>90693</v>
+        <v>94484</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2443,25 +2491,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>2809</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2471,10 +2519,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541639</v>
+        <v>541805</v>
       </c>
       <c r="R17" t="n">
-        <v>7207443</v>
+        <v>7207635</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2506,7 +2554,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2516,7 +2564,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2543,7 +2591,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121087373</v>
+        <v>121087378</v>
       </c>
       <c r="B18" t="n">
         <v>78601</v>
@@ -2583,10 +2631,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541765</v>
+        <v>541709</v>
       </c>
       <c r="R18" t="n">
-        <v>7207564</v>
+        <v>7207545</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2618,7 +2666,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2628,7 +2676,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2655,10 +2703,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121087515</v>
+        <v>121087385</v>
       </c>
       <c r="B19" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2671,45 +2719,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541449</v>
+        <v>541689</v>
       </c>
       <c r="R19" t="n">
-        <v>7207320</v>
+        <v>7207232</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2738,7 +2778,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2748,7 +2788,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2763,22 +2803,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121087382</v>
+        <v>121087380</v>
       </c>
       <c r="B20" t="n">
-        <v>74708</v>
+        <v>90693</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2791,21 +2831,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2815,10 +2855,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541684</v>
+        <v>541639</v>
       </c>
       <c r="R20" t="n">
-        <v>7207277</v>
+        <v>7207443</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2850,7 +2890,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2860,7 +2900,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2887,10 +2927,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121087269</v>
+        <v>121087267</v>
       </c>
       <c r="B21" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2903,21 +2943,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2927,10 +2967,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541501</v>
+        <v>541478</v>
       </c>
       <c r="R21" t="n">
-        <v>7207540</v>
+        <v>7207309</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2962,7 +3002,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2972,7 +3012,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2999,10 +3039,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121087374</v>
+        <v>121087271</v>
       </c>
       <c r="B22" t="n">
-        <v>57351</v>
+        <v>94484</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3011,43 +3051,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541748</v>
+        <v>541696</v>
       </c>
       <c r="R22" t="n">
-        <v>7207555</v>
+        <v>7207589</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3079,7 +3114,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3089,7 +3124,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3116,7 +3151,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121087379</v>
+        <v>121087384</v>
       </c>
       <c r="B23" t="n">
         <v>57351</v>
@@ -3152,7 +3187,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3161,10 +3196,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541665</v>
+        <v>541683</v>
       </c>
       <c r="R23" t="n">
-        <v>7207481</v>
+        <v>7207222</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3196,7 +3231,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3206,7 +3241,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,10 +3268,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121087369</v>
+        <v>121086340</v>
       </c>
       <c r="B24" t="n">
-        <v>57351</v>
+        <v>90983</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3249,42 +3284,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541805</v>
+        <v>541758</v>
       </c>
       <c r="R24" t="n">
-        <v>7207638</v>
+        <v>7207515</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3313,7 +3346,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3323,7 +3356,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>på granlåga med bark</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3332,25 +3370,51 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121087368</v>
+        <v>121087371</v>
       </c>
       <c r="B25" t="n">
         <v>57351</v>
@@ -3386,7 +3450,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3395,10 +3459,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541804</v>
+        <v>541769</v>
       </c>
       <c r="R25" t="n">
-        <v>7207640</v>
+        <v>7207584</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3430,7 +3494,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3440,7 +3504,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3467,10 +3531,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121086345</v>
+        <v>121087269</v>
       </c>
       <c r="B26" t="n">
-        <v>90693</v>
+        <v>90715</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3483,40 +3547,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541754</v>
+        <v>541501</v>
       </c>
       <c r="R26" t="n">
-        <v>7207520</v>
+        <v>7207540</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3545,7 +3606,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3555,12 +3616,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>på levande gran</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3569,54 +3625,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121087371</v>
+        <v>121087376</v>
       </c>
       <c r="B27" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3629,39 +3659,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541769</v>
+        <v>541741</v>
       </c>
       <c r="R27" t="n">
-        <v>7207584</v>
+        <v>7207555</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3693,7 +3718,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3703,7 +3728,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3730,10 +3755,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121087370</v>
+        <v>121087372</v>
       </c>
       <c r="B28" t="n">
-        <v>94484</v>
+        <v>57351</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3742,38 +3767,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541805</v>
+        <v>541765</v>
       </c>
       <c r="R28" t="n">
-        <v>7207635</v>
+        <v>7207562</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3805,7 +3835,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3815,7 +3845,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3842,7 +3872,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121087384</v>
+        <v>121087515</v>
       </c>
       <c r="B29" t="n">
         <v>57351</v>
@@ -3876,24 +3906,27 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541683</v>
+        <v>541449</v>
       </c>
       <c r="R29" t="n">
-        <v>7207222</v>
+        <v>7207320</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3922,7 +3955,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3932,7 +3965,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3947,22 +3980,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121086338</v>
+        <v>121087382</v>
       </c>
       <c r="B30" t="n">
-        <v>57351</v>
+        <v>74708</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3975,45 +4008,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541797</v>
+        <v>541684</v>
       </c>
       <c r="R30" t="n">
-        <v>7207596</v>
+        <v>7207277</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4042,7 +4067,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4052,12 +4077,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4068,36 +4088,16 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 40918-2024 artfynd.xlsx
+++ b/artfynd/A 40918-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121087174</v>
+        <v>121087383</v>
       </c>
       <c r="B2" t="n">
-        <v>90715</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541827</v>
+        <v>541686</v>
       </c>
       <c r="R2" t="n">
-        <v>7207629</v>
+        <v>7207278</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,29 +769,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121087383</v>
+        <v>121087378</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541686</v>
+        <v>541709</v>
       </c>
       <c r="R3" t="n">
-        <v>7207278</v>
+        <v>7207545</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121086338</v>
+        <v>121087367</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>90727</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,45 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541797</v>
+        <v>541803</v>
       </c>
       <c r="R4" t="n">
-        <v>7207596</v>
+        <v>7207639</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,43 +995,23 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121087369</v>
+        <v>121086338</v>
       </c>
       <c r="B5" t="n">
         <v>57351</v>
@@ -1082,24 +1045,27 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541805</v>
+        <v>541797</v>
       </c>
       <c r="R5" t="n">
-        <v>7207638</v>
+        <v>7207596</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1138,7 +1104,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,23 +1120,43 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121087368</v>
+        <v>121087372</v>
       </c>
       <c r="B6" t="n">
         <v>57351</v>
@@ -1201,7 +1192,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1210,10 +1201,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541804</v>
+        <v>541765</v>
       </c>
       <c r="R6" t="n">
-        <v>7207640</v>
+        <v>7207562</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1245,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1255,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121087270</v>
+        <v>121087385</v>
       </c>
       <c r="B7" t="n">
-        <v>90662</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,25 +1285,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1322,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541639</v>
+        <v>541689</v>
       </c>
       <c r="R7" t="n">
-        <v>7207569</v>
+        <v>7207232</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1357,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,7 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121087377</v>
+        <v>121086339</v>
       </c>
       <c r="B8" t="n">
-        <v>90662</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,41 +1397,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541709</v>
+        <v>541803</v>
       </c>
       <c r="R8" t="n">
-        <v>7207545</v>
+        <v>7207589</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,7 +1468,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1478,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,26 +1494,46 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121087373</v>
+        <v>121087270</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>90674</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1518,25 +1542,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1546,10 +1570,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541765</v>
+        <v>541639</v>
       </c>
       <c r="R9" t="n">
-        <v>7207564</v>
+        <v>7207569</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1581,7 +1605,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1591,7 +1615,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,10 +1642,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121087367</v>
+        <v>121087379</v>
       </c>
       <c r="B10" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,34 +1658,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541803</v>
+        <v>541665</v>
       </c>
       <c r="R10" t="n">
-        <v>7207639</v>
+        <v>7207481</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1693,7 +1722,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1703,7 +1732,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121087266</v>
+        <v>121087376</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1770,10 +1799,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541464</v>
+        <v>541741</v>
       </c>
       <c r="R11" t="n">
-        <v>7207278</v>
+        <v>7207555</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1805,7 +1834,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,7 +1844,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121087375</v>
+        <v>121087269</v>
       </c>
       <c r="B12" t="n">
-        <v>90693</v>
+        <v>90727</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,21 +1887,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1882,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541743</v>
+        <v>541501</v>
       </c>
       <c r="R12" t="n">
-        <v>7207555</v>
+        <v>7207540</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1917,7 +1946,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1927,7 +1956,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,7 +1983,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121087379</v>
+        <v>121087371</v>
       </c>
       <c r="B13" t="n">
         <v>57351</v>
@@ -1999,10 +2028,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541665</v>
+        <v>541769</v>
       </c>
       <c r="R13" t="n">
-        <v>7207481</v>
+        <v>7207584</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2034,7 +2063,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2073,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,10 +2100,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121086339</v>
+        <v>121086345</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>90705</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,31 +2116,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2119,10 +2143,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541803</v>
+        <v>541754</v>
       </c>
       <c r="R14" t="n">
-        <v>7207589</v>
+        <v>7207520</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2154,7 +2178,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,12 +2188,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>gamla ringhack</t>
+          <t>på levande gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,6 +2202,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2196,9 +2221,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2216,10 +2246,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121087374</v>
+        <v>121087382</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>74710</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2232,39 +2262,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541748</v>
+        <v>541684</v>
       </c>
       <c r="R15" t="n">
-        <v>7207555</v>
+        <v>7207277</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2296,7 +2321,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2306,7 +2331,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2333,10 +2358,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121086345</v>
+        <v>121087266</v>
       </c>
       <c r="B16" t="n">
-        <v>90693</v>
+        <v>78604</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2349,40 +2374,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541754</v>
+        <v>541464</v>
       </c>
       <c r="R16" t="n">
-        <v>7207520</v>
+        <v>7207278</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2411,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2421,12 +2443,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>på levande gran</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2435,54 +2452,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121087370</v>
+        <v>121086340</v>
       </c>
       <c r="B17" t="n">
-        <v>94484</v>
+        <v>90995</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2491,41 +2482,44 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541805</v>
+        <v>541758</v>
       </c>
       <c r="R17" t="n">
-        <v>7207635</v>
+        <v>7207515</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2554,7 +2548,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2564,7 +2558,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>på granlåga med bark</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2573,28 +2572,54 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121087378</v>
+        <v>121087375</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>90705</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2607,21 +2632,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2631,10 +2656,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541709</v>
+        <v>541743</v>
       </c>
       <c r="R18" t="n">
-        <v>7207545</v>
+        <v>7207555</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2666,7 +2691,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2676,7 +2701,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2703,10 +2728,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121087385</v>
+        <v>121087174</v>
       </c>
       <c r="B19" t="n">
-        <v>78601</v>
+        <v>90727</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2719,37 +2744,40 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541689</v>
+        <v>541827</v>
       </c>
       <c r="R19" t="n">
-        <v>7207232</v>
+        <v>7207629</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2778,7 +2806,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2788,7 +2816,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2797,28 +2825,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121087380</v>
+        <v>121087267</v>
       </c>
       <c r="B20" t="n">
-        <v>90693</v>
+        <v>78604</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2831,21 +2860,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2855,10 +2884,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541639</v>
+        <v>541478</v>
       </c>
       <c r="R20" t="n">
-        <v>7207443</v>
+        <v>7207309</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2890,7 +2919,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2900,7 +2929,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2927,10 +2956,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121087267</v>
+        <v>121087373</v>
       </c>
       <c r="B21" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2967,10 +2996,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541478</v>
+        <v>541765</v>
       </c>
       <c r="R21" t="n">
-        <v>7207309</v>
+        <v>7207564</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3002,7 +3031,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3012,7 +3041,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3039,10 +3068,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121087271</v>
+        <v>121087370</v>
       </c>
       <c r="B22" t="n">
-        <v>94484</v>
+        <v>94496</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3079,10 +3108,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541696</v>
+        <v>541805</v>
       </c>
       <c r="R22" t="n">
-        <v>7207589</v>
+        <v>7207635</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3114,7 +3143,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3124,7 +3153,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3268,10 +3297,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121086340</v>
+        <v>121087368</v>
       </c>
       <c r="B24" t="n">
-        <v>90983</v>
+        <v>57351</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3284,40 +3313,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541758</v>
+        <v>541804</v>
       </c>
       <c r="R24" t="n">
-        <v>7207515</v>
+        <v>7207640</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3346,7 +3377,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3356,12 +3387,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:56</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>på granlåga med bark</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3370,54 +3396,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121087371</v>
+        <v>121087271</v>
       </c>
       <c r="B25" t="n">
-        <v>57351</v>
+        <v>94496</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3426,43 +3426,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541769</v>
+        <v>541696</v>
       </c>
       <c r="R25" t="n">
-        <v>7207584</v>
+        <v>7207589</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3494,7 +3489,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3504,7 +3499,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3531,10 +3526,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121087269</v>
+        <v>121087377</v>
       </c>
       <c r="B26" t="n">
-        <v>90715</v>
+        <v>90674</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3543,25 +3538,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3571,10 +3566,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541501</v>
+        <v>541709</v>
       </c>
       <c r="R26" t="n">
-        <v>7207540</v>
+        <v>7207545</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3606,7 +3601,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3616,7 +3611,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3643,10 +3638,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121087376</v>
+        <v>121087374</v>
       </c>
       <c r="B27" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3659,31 +3654,36 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541741</v>
+        <v>541748</v>
       </c>
       <c r="R27" t="n">
         <v>7207555</v>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3755,10 +3755,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121087372</v>
+        <v>121087380</v>
       </c>
       <c r="B28" t="n">
-        <v>57351</v>
+        <v>90705</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3771,39 +3771,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541765</v>
+        <v>541639</v>
       </c>
       <c r="R28" t="n">
-        <v>7207562</v>
+        <v>7207443</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3835,7 +3830,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3845,7 +3840,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3872,7 +3867,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121087515</v>
+        <v>121087369</v>
       </c>
       <c r="B29" t="n">
         <v>57351</v>
@@ -3906,27 +3901,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541449</v>
+        <v>541805</v>
       </c>
       <c r="R29" t="n">
-        <v>7207320</v>
+        <v>7207638</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3955,7 +3947,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3965,7 +3957,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3980,22 +3972,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121087382</v>
+        <v>121087515</v>
       </c>
       <c r="B30" t="n">
-        <v>74708</v>
+        <v>57351</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4008,37 +4000,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541684</v>
+        <v>541449</v>
       </c>
       <c r="R30" t="n">
-        <v>7207277</v>
+        <v>7207320</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4092,12 +4092,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 40918-2024 artfynd.xlsx
+++ b/artfynd/A 40918-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121087383</v>
+        <v>121087267</v>
       </c>
       <c r="B2" t="n">
         <v>78604</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541686</v>
+        <v>541478</v>
       </c>
       <c r="R2" t="n">
-        <v>7207278</v>
+        <v>7207309</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121087367</v>
+        <v>121087372</v>
       </c>
       <c r="B4" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541803</v>
+        <v>541765</v>
       </c>
       <c r="R4" t="n">
-        <v>7207639</v>
+        <v>7207562</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121086338</v>
+        <v>121087384</v>
       </c>
       <c r="B5" t="n">
         <v>57351</v>
@@ -1045,27 +1050,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541797</v>
+        <v>541683</v>
       </c>
       <c r="R5" t="n">
-        <v>7207596</v>
+        <v>7207222</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,46 +1117,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121087372</v>
+        <v>121086345</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>90706</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,42 +1149,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541765</v>
+        <v>541754</v>
       </c>
       <c r="R6" t="n">
-        <v>7207562</v>
+        <v>7207520</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,24 +1224,55 @@
           <t>09:53</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på levande gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1385,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121086339</v>
+        <v>121087382</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>74710</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,45 +1407,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541803</v>
+        <v>541684</v>
       </c>
       <c r="R8" t="n">
-        <v>7207589</v>
+        <v>7207277</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1468,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,12 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>gamla ringhack</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,46 +1487,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121087270</v>
+        <v>121087374</v>
       </c>
       <c r="B9" t="n">
-        <v>90674</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,38 +1515,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541639</v>
+        <v>541748</v>
       </c>
       <c r="R9" t="n">
-        <v>7207569</v>
+        <v>7207555</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1605,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1615,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121087379</v>
+        <v>121087367</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,39 +1636,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541665</v>
+        <v>541803</v>
       </c>
       <c r="R10" t="n">
-        <v>7207481</v>
+        <v>7207639</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1722,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1732,7 +1705,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121087376</v>
+        <v>121087368</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1775,34 +1748,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541741</v>
+        <v>541804</v>
       </c>
       <c r="R11" t="n">
-        <v>7207555</v>
+        <v>7207640</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1834,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1844,7 +1822,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,10 +1849,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121087269</v>
+        <v>121086339</v>
       </c>
       <c r="B12" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,37 +1865,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541501</v>
+        <v>541803</v>
       </c>
       <c r="R12" t="n">
-        <v>7207540</v>
+        <v>7207589</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1946,7 +1932,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1956,7 +1942,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1967,26 +1958,46 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121087371</v>
+        <v>121087376</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,39 +2010,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541769</v>
+        <v>541741</v>
       </c>
       <c r="R13" t="n">
-        <v>7207584</v>
+        <v>7207555</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2063,7 +2069,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2073,7 +2079,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2100,10 +2106,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121086345</v>
+        <v>121087377</v>
       </c>
       <c r="B14" t="n">
-        <v>90705</v>
+        <v>90675</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2112,44 +2118,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541754</v>
+        <v>541709</v>
       </c>
       <c r="R14" t="n">
-        <v>7207520</v>
+        <v>7207545</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2178,7 +2181,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2188,12 +2191,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>på levande gran</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2202,54 +2200,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121087382</v>
+        <v>121087269</v>
       </c>
       <c r="B15" t="n">
-        <v>74710</v>
+        <v>90728</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2262,21 +2234,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2286,10 +2258,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541684</v>
+        <v>541501</v>
       </c>
       <c r="R15" t="n">
-        <v>7207277</v>
+        <v>7207540</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2321,7 +2293,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2331,7 +2303,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2358,7 +2330,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121087266</v>
+        <v>121087373</v>
       </c>
       <c r="B16" t="n">
         <v>78604</v>
@@ -2398,10 +2370,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541464</v>
+        <v>541765</v>
       </c>
       <c r="R16" t="n">
-        <v>7207278</v>
+        <v>7207564</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2433,7 +2405,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2443,7 +2415,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121086340</v>
+        <v>121087370</v>
       </c>
       <c r="B17" t="n">
-        <v>90995</v>
+        <v>94497</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2482,44 +2454,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rödingsjön, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541758</v>
+        <v>541805</v>
       </c>
       <c r="R17" t="n">
-        <v>7207515</v>
+        <v>7207635</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2548,7 +2517,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2558,12 +2527,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:56</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>på granlåga med bark</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2572,54 +2536,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Mårtensson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121087375</v>
+        <v>121087379</v>
       </c>
       <c r="B18" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,34 +2570,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541743</v>
+        <v>541665</v>
       </c>
       <c r="R18" t="n">
-        <v>7207555</v>
+        <v>7207481</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2691,7 +2634,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2701,7 +2644,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2728,10 +2671,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121087174</v>
+        <v>121086338</v>
       </c>
       <c r="B19" t="n">
-        <v>90727</v>
+        <v>57351</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2744,40 +2687,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541827</v>
+        <v>541797</v>
       </c>
       <c r="R19" t="n">
-        <v>7207629</v>
+        <v>7207596</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2806,7 +2754,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2816,7 +2764,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>gamla ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2825,29 +2778,48 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121087267</v>
+        <v>121087371</v>
       </c>
       <c r="B20" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2860,34 +2832,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541478</v>
+        <v>541769</v>
       </c>
       <c r="R20" t="n">
-        <v>7207309</v>
+        <v>7207584</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2919,7 +2896,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2929,7 +2906,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2956,10 +2933,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121087373</v>
+        <v>121087380</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
+        <v>90706</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2972,21 +2949,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2996,10 +2973,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541765</v>
+        <v>541639</v>
       </c>
       <c r="R21" t="n">
-        <v>7207564</v>
+        <v>7207443</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3031,7 +3008,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3041,7 +3018,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3068,10 +3045,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121087370</v>
+        <v>121087383</v>
       </c>
       <c r="B22" t="n">
-        <v>94496</v>
+        <v>78604</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3080,25 +3057,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3108,10 +3085,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541805</v>
+        <v>541686</v>
       </c>
       <c r="R22" t="n">
-        <v>7207635</v>
+        <v>7207278</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3143,7 +3120,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3153,7 +3130,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3180,10 +3157,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121087384</v>
+        <v>121086340</v>
       </c>
       <c r="B23" t="n">
-        <v>57351</v>
+        <v>90996</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3196,42 +3173,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjön, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541683</v>
+        <v>541758</v>
       </c>
       <c r="R23" t="n">
-        <v>7207222</v>
+        <v>7207515</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3260,7 +3235,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3270,7 +3245,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>på granlåga med bark</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3279,28 +3259,54 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Eva Mårtensson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Eva Mårtensson, Isak Vahlström, Nils Åslund</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121087368</v>
+        <v>121087271</v>
       </c>
       <c r="B24" t="n">
-        <v>57351</v>
+        <v>94497</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3309,43 +3315,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541804</v>
+        <v>541696</v>
       </c>
       <c r="R24" t="n">
-        <v>7207640</v>
+        <v>7207589</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3377,7 +3378,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3387,7 +3388,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3414,10 +3415,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121087271</v>
+        <v>121087515</v>
       </c>
       <c r="B25" t="n">
-        <v>94496</v>
+        <v>57351</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3426,41 +3427,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541696</v>
+        <v>541449</v>
       </c>
       <c r="R25" t="n">
-        <v>7207589</v>
+        <v>7207320</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3489,7 +3498,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3499,7 +3508,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3514,22 +3523,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121087377</v>
+        <v>121087174</v>
       </c>
       <c r="B26" t="n">
-        <v>90674</v>
+        <v>90728</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3538,41 +3547,44 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rödingtjärnen, Ås lm</t>
+          <t>Rödingsjötjärn, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541709</v>
+        <v>541827</v>
       </c>
       <c r="R26" t="n">
-        <v>7207545</v>
+        <v>7207629</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3601,7 +3613,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3611,7 +3623,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3620,28 +3632,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
+          <t>Nils Åslund</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121087374</v>
+        <v>121087375</v>
       </c>
       <c r="B27" t="n">
-        <v>57351</v>
+        <v>90706</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3654,36 +3667,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541748</v>
+        <v>541743</v>
       </c>
       <c r="R27" t="n">
         <v>7207555</v>
@@ -3718,7 +3726,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3728,7 +3736,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3755,10 +3763,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121087380</v>
+        <v>121087369</v>
       </c>
       <c r="B28" t="n">
-        <v>90705</v>
+        <v>57351</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3771,34 +3779,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541639</v>
+        <v>541805</v>
       </c>
       <c r="R28" t="n">
-        <v>7207443</v>
+        <v>7207638</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3830,7 +3843,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3840,7 +3853,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3867,10 +3880,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121087369</v>
+        <v>121087270</v>
       </c>
       <c r="B29" t="n">
-        <v>57351</v>
+        <v>90675</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3879,43 +3892,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541805</v>
+        <v>541639</v>
       </c>
       <c r="R29" t="n">
-        <v>7207638</v>
+        <v>7207569</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3947,7 +3955,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3957,7 +3965,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3984,10 +3992,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121087515</v>
+        <v>121087266</v>
       </c>
       <c r="B30" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4000,45 +4008,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rödingsjötjärn, Ås lm</t>
+          <t>Rödingtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541449</v>
+        <v>541464</v>
       </c>
       <c r="R30" t="n">
-        <v>7207320</v>
+        <v>7207278</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4092,12 +4092,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Nils Åslund</t>
+          <t>Isak Vahlström, Eva Mårtensson, Nils Åslund, johan åslund</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
